--- a/output/final_submission_audit.xlsx
+++ b/output/final_submission_audit.xlsx
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12 slides with rich speaker notes and epistemological labels.</t>
+          <t>14 slides with rich speaker notes and epistemological labels.</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹1,365.42 Cr</t>
+          <t>₹131.09 Cr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2,402 (23.5%)</t>
+          <t>2,402 (23.55%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹337.89 Cr (24.7%)</t>
+          <t>₹67.33 Cr (51.37%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹162.24 Cr (48.0%)</t>
+          <t>₹39.73 Cr (61.00%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zero inflation: 10,200 rows with ₹1,365.42 Cr matches raw accounts exactly.</t>
+          <t>Zero inflation: 10,200 rows with ₹131.09 Cr matches raw accounts exactly.</t>
         </is>
       </c>
     </row>
